--- a/GC-BUILD-STATE.xlsx
+++ b/GC-BUILD-STATE.xlsx
@@ -2745,10 +2745,10 @@
     <t xml:space="preserve">D-11</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirm the production domain.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">getawaycollective.in is assumed throughout .env.example. Every share card and sitemap URL depends on it.</t>
+    <t xml:space="preserve">ANSWERED 1 Aug 2026: the domain is getawaycollective.co (www 301s to the apex). The code now carries it. REMAINING: the domain currently serves a GoDaddy Website Builder page — DNS must be repointed to Vercel at go-live, and the builder page retired.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set NEXT_PUBLIC_SITE_URL=https://getawaycollective.co in Vercel. Decide the cutover moment: repointing DNS replaces the current GoDaddy page immediately.</t>
   </si>
   <si>
     <t xml:space="preserve">D-12</t>
@@ -15063,7 +15063,7 @@
       </c>
       <c r="I14" s="24"/>
     </row>
-    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
         <v>888</v>
       </c>

--- a/GC-BUILD-STATE.xlsx
+++ b/GC-BUILD-STATE.xlsx
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3098" uniqueCount="1317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3098" uniqueCount="1319">
   <si>
     <t xml:space="preserve">Getaway Collective · Build State</t>
   </si>
@@ -1695,7 +1695,7 @@
     <t xml:space="preserve">Read the Terms and Conditions button</t>
   </si>
   <si>
-    <t xml:space="preserve">Renders the full T&amp;C document over the form. Gates the agreement checkbox — the box enables only once the document has been opened.</t>
+    <t xml:space="preserve">Renders the full T&amp;C document over the form. Gates the agreement checkbox.</t>
   </si>
   <si>
     <t xml:space="preserve">Paper</t>
@@ -1704,7 +1704,7 @@
     <t xml:space="preserve">Code</t>
   </si>
   <si>
-    <t xml:space="preserve">app/_assemblies/flow.tsx:577. Opens IN PLACE rather than linking away: a link loses the half-filled application. Does NOT require scrolling to the end — scroll position is not reading, and a keyboard user never fires a scroll handler.</t>
+    <t xml:space="preserve">app/_assemblies/flow.tsx. Opens IN PLACE; does not require scrolling — scroll position is not reading.</t>
   </si>
   <si>
     <t xml:space="preserve">P-02</t>
@@ -1719,7 +1719,7 @@
     <t xml:space="preserve">Void</t>
   </si>
   <si>
-    <t xml:space="preserve">app/_assemblies/gatewaypages.tsx:229. Close is never hover-revealed and never in a vanishing corner.</t>
+    <t xml:space="preserve">app/_assemblies/gatewaypages.tsx.</t>
   </si>
   <si>
     <t xml:space="preserve">P-03</t>
@@ -1731,445 +1731,451 @@
     <t xml:space="preserve">First visit</t>
   </si>
   <si>
-    <t xml:space="preserve">Cookie / consent banner.</t>
+    <t xml:space="preserve">Cookie / consent banner. A banner, not a modal — DECLINE IS THE PRIMARY ACTION.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">app/_assemblies/dialogs.tsx, mounted in the root layout. States honestly that no non-essential storage exists in this build. Choice persists in localStorage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reload / tab close mid-form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unsaved-changes guard via beforeunload.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">useUnsavedGuard in dialogs.tsx. Boundary stated in code: fields autosave on blur, so only the field being typed is at risk; in-app navigation keeps drafts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any authenticated surface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session nearing expiry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session-expiry dialog with extend control.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component ready; no live mount because no session exists. Reviewable on any page via ?specimen=session. Wires to Clerk when identity connects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle console · Resolutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cast a vote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vote confirmation: the 3-second piston, weight and threshold stated, ADR-0008 sealing stated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mounted on a SPECIMEN ballot in the console (marked, casts nothing). The dialog is the real one; the register is honestly empty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registration dialog with kind (no default), licence and file. Inline form also retained.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byte upload still blocked on Vercel Blob and says so. ?specimen=upload.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit formation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm requires the Board RESOLUTION REFERENCE (R-YYYY-NN), not a click.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mounted at the end of the formation stepper. Nothing writes; the dialog says so.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A destructive act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type-the-exact-name + recorded reason (E-02) to enable the control. Never the default, never autofocused.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mounted on Withdraw-a-plate in /admin/media (specimen) and via ?specimen=destructive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NONE, deliberately.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The commitment is the piston; a confirm dialog after a hold would be two confirmations, training people to dismiss both.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-Product Notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two routes exist to HOLD notifications; no notification is generated by anything. Every row below is Proposed unless marked otherwise. The trigger column names the event — a notification without a named event is a notification nobody can test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event that fires it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urgency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where it lands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(the surfaces that hold them)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/member/notifications, /member/settings/notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The feed renders the full catalogue as marked SPECIMENS (app/_assemblies/notices.tsx); settings is composed. Nothing writes to them yet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accreditation submitted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application received. A decision follows within 15 working days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applicant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email + in-product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Designed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wording lives in content/notifications.ts (N-01) and renders as a specimen in the feed. Event source not wired.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accreditation decided</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accreditation approved / declined, with the reason.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A decline must state a reason and a route to appeal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deposit received</t>
+  </si>
+  <si>
+    <t xml:space="preserve">₹50,000 received. It holds your position; it does not make you a partner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must repeat the Member Law. The commonest misreading of a deposit is that it completes the purchase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completion window opening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance and Vehicle Agreement due within 15 working days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs a countdown, and a second at T-3 days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SETTLEMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You are a Member of &lt;vehicle&gt;. Entitlement and governance rights begin now.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE MEMBER LAW (I-08) fires here and only here. This is the single most important notification in the system and it is irreversible.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolution opened</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A resolution is open for your vote. Threshold: ordinary / special. Closes &lt;date&gt;.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must state the threshold and the voting weight, per §24a.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolution closing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your vote has not been cast. Voting closes in 48 hours.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A tie is NOT approval, so an uncast vote has a real consequence and the reminder must say so.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolution decided</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outcome, the count, and the threshold it met.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-0008: secret ballot, transparent outcome. Publish the tally, never who voted how.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution declared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;amount&gt; declared for the period ending &lt;date&gt;.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must carry a confidence class like every other figure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution paid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;amount&gt; paid to the account ending &lt;n&gt;.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution BLOCKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No distribution this period. Stage six does not run if the reserve would fall below its floor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silence here reads as an error. A profitable period with no distribution is normal and must be explained when it happens, not in a FAQ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entitlement opens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your &lt;n&gt; nights for &lt;year&gt; are now drawable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not before handover — nothing is drawable against an unbuilt asset.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entitlement expiring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;n&gt; nights lapse on &lt;date&gt;.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs a stated lapse policy first — see Decisions D-07.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document version changed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;document&gt; is now v&lt;n&gt;. What changed: &lt;summary&gt;.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A binding document changing under someone silently is the failure mode. Must link the diff.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covenant proximity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSCR approaching the covenant threshold.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office vantage only. Never shown at member vantage without Board sign-off on the wording.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valuation published</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;property&gt; revalued to &lt;amount&gt; by &lt;source&gt;.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must name the source and its confidence class; a management estimate is not an appraisal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead captured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A signal / dossier request arrived.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The only notification that actually fires today. app/api/signal, app/api/dossier → lib/leads.ts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transactional Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two endpoints are live via Resend; both return 503 without RESEND_API_KEY and the page says so rather than showing a false success. Everything else is proposed. No template system, no unsubscribe handling and no verified sending domain exists yet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subject / purpose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/signal form submit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIGNAL_LEAD_EMAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Signal subscriber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plain text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lib/leads.ts. Returns 503 when unconfigured; the form renders an honest failure with a mailto fallback.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/communique/request submit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOSSIER_LEAD_EMAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New dossier request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same path. 400 on invalid input, 503 on unconfigured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signal form submit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The subscriber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm the subscription (double opt-in)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outbound</t>
   </si>
   <si>
     <t xml:space="preserve">Proposed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/legal/cookies exists as a document with no banner in front of it. REQUIRED for DPDP and GDPR if you take EU traffic. Must default to declining non-essential.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigating away mid-form</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unsaved-changes guard.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The form autosaves on blur, so this is lower risk than usual — but a half-finished PAN field is lost on a back button today.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any authenticated surface</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Session nearing expiry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Session-expiry warning with an extend control.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blocked: no authentication exists. Build with Clerk, not before.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cast a vote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vote confirmation. Contribution-weighted, irreversible, and states the weight being cast.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A vote is irreversible under §24a. It needs the same deliberation treatment as the commitment piston, not an OK button.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File picker with type, dimension and licence capture.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The media admin surface is built; the upload path is not. Blocked on Vercel Blob.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submit formation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm-before-create for a new LLP.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creates a constitutional entity. Should require a resolution reference, not a click.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A destructive admin action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm-destructive dialog. Types the object name to confirm.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No destructive admin action is wired yet, so nothing is at risk today.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NONE, deliberately.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The commitment is a 3-second sustained press (the piston), not a dialog. The duration IS the deliberation. A confirm dialog after a hold would be two confirmations, which trains people to dismiss both.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-Product Notifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two routes exist to HOLD notifications; no notification is generated by anything. Every row below is Proposed unless marked otherwise. The trigger column names the event — a notification without a named event is a notification nobody can test.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Event that fires it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Message</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Audience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urgency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where it lands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(the surfaces that hold them)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Member</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/member/notifications, /member/settings/notifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both routes exist and render the registry Surface. Nothing writes to them.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accreditation submitted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application received. A decision follows within 15 working days.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applicant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Normal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email + in-product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PR-01 states the window; nothing currently confirms receipt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accreditation decided</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accreditation approved / declined, with the reason.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A decline must state a reason and a route to appeal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deposit received</t>
-  </si>
-  <si>
-    <t xml:space="preserve">₹50,000 received. It holds your position; it does not make you a partner.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Investor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must repeat the Member Law. The commonest misreading of a deposit is that it completes the purchase.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completion window opening</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balance and Vehicle Agreement due within 15 working days.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs a countdown, and a second at T-3 days.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SETTLEMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You are a Member of &lt;vehicle&gt;. Entitlement and governance rights begin now.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Critical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THE MEMBER LAW (I-08) fires here and only here. This is the single most important notification in the system and it is irreversible.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resolution opened</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A resolution is open for your vote. Threshold: ordinary / special. Closes &lt;date&gt;.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must state the threshold and the voting weight, per §24a.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resolution closing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your vote has not been cast. Voting closes in 48 hours.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A tie is NOT approval, so an uncast vote has a real consequence and the reminder must say so.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resolution decided</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outcome, the count, and the threshold it met.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-0008: secret ballot, transparent outcome. Publish the tally, never who voted how.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distribution declared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;amount&gt; declared for the period ending &lt;date&gt;.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must carry a confidence class like every other figure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distribution paid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;amount&gt; paid to the account ending &lt;n&gt;.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distribution BLOCKED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No distribution this period. Stage six does not run if the reserve would fall below its floor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silence here reads as an error. A profitable period with no distribution is normal and must be explained when it happens, not in a FAQ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entitlement opens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your &lt;n&gt; nights for &lt;year&gt; are now drawable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not before handover — nothing is drawable against an unbuilt asset.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entitlement expiring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;n&gt; nights lapse on &lt;date&gt;.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs a stated lapse policy first — see Decisions D-07.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document version changed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;document&gt; is now v&lt;n&gt;. What changed: &lt;summary&gt;.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A binding document changing under someone silently is the failure mode. Must link the diff.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covenant proximity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSCR approaching the covenant threshold.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Office vantage only. Never shown at member vantage without Board sign-off on the wording.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valuation published</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;property&gt; revalued to &lt;amount&gt; by &lt;source&gt;.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must name the source and its confidence class; a management estimate is not an appraisal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead captured</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A signal / dossier request arrived.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The only notification that actually fires today. app/api/signal, app/api/dossier → lib/leads.ts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transactional Email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two endpoints are live via Resend; both return 503 without RESEND_API_KEY and the page says so rather than showing a false success. Everything else is proposed. No template system, no unsubscribe handling and no verified sending domain exists yet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subject / purpose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Template</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/signal form submit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIGNAL_LEAD_EMAIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Signal subscriber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plain text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lib/leads.ts. Returns 503 when unconfigured; the form renders an honest failure with a mailto fallback.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/communique/request submit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOSSIER_LEAD_EMAIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New dossier request</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same path. 400 on invalid input, 503 on unconfigured.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signal form submit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The subscriber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm the subscription (double opt-in)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outbound</t>
   </si>
   <si>
     <t xml:space="preserve">REQUIRED. Today you capture an address and send that person nothing — no confirmation and no way to unsubscribe. This is a compliance gap, not a nicety.</t>
@@ -4289,11 +4295,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4813,12 +4819,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -4829,25 +4835,25 @@
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4855,7 +4861,7 @@
         <v>222</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="C5" s="27"/>
       <c r="D5" s="27"/>
@@ -4866,35 +4872,35 @@
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13"/>
       <c r="B6" s="13" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>242</v>
       </c>
       <c r="F6" s="15"/>
       <c r="G6" s="15" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13"/>
       <c r="B7" s="13" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
@@ -4902,285 +4908,285 @@
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13"/>
       <c r="B8" s="13" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>242</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13"/>
       <c r="B9" s="13" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="15" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13"/>
       <c r="B10" s="13" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13"/>
       <c r="B11" s="13" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>1071</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>1072</v>
+        <v>1073</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="G11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13"/>
       <c r="B12" s="13" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>1072</v>
+        <v>1078</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="G12" s="15"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13"/>
       <c r="B13" s="13" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C13" s="13" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>1079</v>
       </c>
-      <c r="D13" s="22" t="s">
-        <v>1072</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>1077</v>
-      </c>
       <c r="F13" s="15" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="G13" s="15"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13"/>
       <c r="B14" s="13" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>1072</v>
+        <v>1083</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="G14" s="15"/>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13"/>
       <c r="B15" s="13" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>1072</v>
+        <v>1085</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="G15" s="15"/>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13"/>
       <c r="B16" s="13" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>1086</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>1072</v>
+        <v>1088</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="G16" s="15"/>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13"/>
       <c r="B17" s="13" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13"/>
       <c r="B18" s="13" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>1072</v>
+        <v>1094</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="G18" s="15"/>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13"/>
       <c r="B19" s="13" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>1094</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>1072</v>
+        <v>1096</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="G19" s="15"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13"/>
       <c r="B20" s="13" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>1072</v>
+        <v>1098</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="G20" s="15"/>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13"/>
       <c r="B21" s="13" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>1098</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>1072</v>
+        <v>1100</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="G21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13"/>
       <c r="B22" s="13" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>1100</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>1072</v>
+        <v>1102</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="G22" s="15"/>
     </row>
@@ -5189,7 +5195,7 @@
         <v>234</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="C23" s="27"/>
       <c r="D23" s="27"/>
@@ -5200,184 +5206,184 @@
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13"/>
       <c r="B24" s="13" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>1072</v>
+        <v>1106</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="G24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13"/>
       <c r="B25" s="13" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="C25" s="13" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E25" s="15" t="s">
         <v>1107</v>
       </c>
-      <c r="D25" s="22" t="s">
-        <v>1072</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>1105</v>
-      </c>
       <c r="F25" s="15" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="G25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13"/>
       <c r="B26" s="13" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="15" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13"/>
       <c r="B27" s="13" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="F27" s="15"/>
       <c r="G27" s="15" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13"/>
       <c r="B28" s="13" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="F28" s="15"/>
       <c r="G28" s="15" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13"/>
       <c r="B29" s="13" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>1072</v>
+        <v>1122</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="G29" s="15"/>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13"/>
       <c r="B30" s="13" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="C30" s="13" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E30" s="15" t="s">
         <v>1123</v>
       </c>
-      <c r="D30" s="22" t="s">
-        <v>1072</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>1121</v>
-      </c>
       <c r="F30" s="15" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="G30" s="15"/>
     </row>
     <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13"/>
       <c r="B31" s="13" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="15" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="G31" s="15"/>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13"/>
       <c r="B32" s="13" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D32" s="20" t="s">
         <v>1129</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>1127</v>
       </c>
       <c r="E32" s="15"/>
       <c r="F32" s="15" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="G32" s="15"/>
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13"/>
       <c r="B33" s="13" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="15" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="G33" s="15"/>
     </row>
@@ -5386,7 +5392,7 @@
         <v>248</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="C34" s="27"/>
       <c r="D34" s="27"/>
@@ -5397,16 +5403,16 @@
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13"/>
       <c r="B35" s="13" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F35" s="15"/>
       <c r="G35" s="15"/>
@@ -5414,54 +5420,54 @@
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13"/>
       <c r="B36" s="13" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="F36" s="15"/>
       <c r="G36" s="15" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13"/>
       <c r="B37" s="13" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>1141</v>
-      </c>
-      <c r="D37" s="22" t="s">
-        <v>1072</v>
+        <v>1143</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="G37" s="15"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13"/>
       <c r="B38" s="13" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="F38" s="15"/>
       <c r="G38" s="15"/>
@@ -5469,16 +5475,16 @@
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13"/>
       <c r="B39" s="13" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="F39" s="15"/>
       <c r="G39" s="15"/>
@@ -5486,32 +5492,32 @@
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13"/>
       <c r="B40" s="13" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="F40" s="15"/>
       <c r="G40" s="15" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13"/>
       <c r="B41" s="13" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>270</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>359</v>
@@ -5522,292 +5528,292 @@
     <row r="42" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13"/>
       <c r="B42" s="13" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>1152</v>
-      </c>
-      <c r="D42" s="22" t="s">
-        <v>1072</v>
+        <v>1154</v>
+      </c>
+      <c r="D42" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="G42" s="15"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13"/>
       <c r="B43" s="13" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="C43" s="13" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E43" s="15" t="s">
         <v>1155</v>
       </c>
-      <c r="D43" s="22" t="s">
-        <v>1072</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>1153</v>
-      </c>
       <c r="F43" s="15" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="G43" s="15"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13"/>
       <c r="B44" s="13" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D44" s="22" t="s">
-        <v>1072</v>
+        <v>1159</v>
+      </c>
+      <c r="D44" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="G44" s="15"/>
     </row>
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13"/>
       <c r="B45" s="13" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>1158</v>
-      </c>
-      <c r="D45" s="22" t="s">
-        <v>1072</v>
+        <v>1160</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="G45" s="15"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13"/>
       <c r="B46" s="13" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>1162</v>
-      </c>
-      <c r="D46" s="22" t="s">
-        <v>1072</v>
+        <v>1164</v>
+      </c>
+      <c r="D46" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="G46" s="15"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13"/>
       <c r="B47" s="13" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="C47" s="13" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D47" s="23" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E47" s="15" t="s">
         <v>1165</v>
       </c>
-      <c r="D47" s="22" t="s">
-        <v>1072</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>1163</v>
-      </c>
       <c r="F47" s="15" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="G47" s="15"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13"/>
       <c r="B48" s="13" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>1167</v>
-      </c>
-      <c r="D48" s="22" t="s">
-        <v>1072</v>
+        <v>1169</v>
+      </c>
+      <c r="D48" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G48" s="15"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13"/>
       <c r="B49" s="13" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>1169</v>
-      </c>
-      <c r="D49" s="22" t="s">
-        <v>1072</v>
+        <v>1171</v>
+      </c>
+      <c r="D49" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="G49" s="15"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="13"/>
       <c r="B50" s="13" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>1072</v>
+        <v>1174</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="G50" s="15"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="13"/>
       <c r="B51" s="13" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>1174</v>
-      </c>
-      <c r="D51" s="22" t="s">
-        <v>1072</v>
+        <v>1176</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="G51" s="15"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="13"/>
       <c r="B52" s="13" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>445</v>
       </c>
-      <c r="D52" s="22" t="s">
-        <v>1072</v>
+      <c r="D52" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="G52" s="15"/>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="13"/>
       <c r="B53" s="13" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>1086</v>
-      </c>
-      <c r="D53" s="22" t="s">
-        <v>1072</v>
+        <v>1088</v>
+      </c>
+      <c r="D53" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="G53" s="15"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="13"/>
       <c r="B54" s="13" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>1178</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>1072</v>
+        <v>1180</v>
+      </c>
+      <c r="D54" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="G54" s="15"/>
     </row>
     <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="13"/>
       <c r="B55" s="13" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="D55" s="13" t="s">
         <v>212</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="F55" s="15"/>
       <c r="G55" s="15" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="13"/>
       <c r="B56" s="13" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="F56" s="15"/>
       <c r="G56" s="15" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="13"/>
       <c r="B57" s="13" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="C57" s="13" t="s">
         <v>302</v>
@@ -5816,7 +5822,7 @@
         <v>212</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="F57" s="15"/>
       <c r="G57" s="15"/>
@@ -5824,16 +5830,16 @@
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="13"/>
       <c r="B58" s="13" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="F58" s="15"/>
       <c r="G58" s="15"/>
@@ -5841,13 +5847,13 @@
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="13"/>
       <c r="B59" s="13" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E59" s="15" t="s">
         <v>278</v>
@@ -5858,16 +5864,16 @@
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="13"/>
       <c r="B60" s="13" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="F60" s="15"/>
       <c r="G60" s="15"/>
@@ -5875,35 +5881,35 @@
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="13"/>
       <c r="B61" s="13" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="F61" s="15"/>
       <c r="G61" s="15" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="13"/>
       <c r="B62" s="13" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="C62" s="13" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D62" s="14" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E62" s="15" t="s">
         <v>1199</v>
-      </c>
-      <c r="D62" s="14" t="s">
-        <v>1059</v>
-      </c>
-      <c r="E62" s="15" t="s">
-        <v>1197</v>
       </c>
       <c r="F62" s="15"/>
       <c r="G62" s="15"/>
@@ -5911,16 +5917,16 @@
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="13"/>
       <c r="B63" s="13" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="F63" s="15"/>
       <c r="G63" s="15"/>
@@ -5928,47 +5934,47 @@
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="13"/>
       <c r="B64" s="13" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>1141</v>
-      </c>
-      <c r="D64" s="22" t="s">
-        <v>1072</v>
+        <v>1143</v>
+      </c>
+      <c r="D64" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="G64" s="15"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="13"/>
       <c r="B65" s="13" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="F65" s="15"/>
       <c r="G65" s="15" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="26" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="B66" s="27" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="C66" s="27"/>
       <c r="D66" s="27"/>
@@ -5979,73 +5985,73 @@
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="13"/>
       <c r="B67" s="13" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="F67" s="15"/>
       <c r="G67" s="15" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="13"/>
       <c r="B68" s="13" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F68" s="15"/>
       <c r="G68" s="15" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="13"/>
       <c r="B69" s="13" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>212</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="F69" s="15"/>
       <c r="G69" s="15" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="13"/>
       <c r="B70" s="13" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="F70" s="15"/>
       <c r="G70" s="15"/>
@@ -6053,13 +6059,13 @@
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="13"/>
       <c r="B71" s="13" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E71" s="15" t="s">
         <v>488</v>
@@ -6070,225 +6076,225 @@
     <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="13"/>
       <c r="B72" s="13" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>212</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="F72" s="15"/>
       <c r="G72" s="15" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="13"/>
       <c r="B73" s="13" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F73" s="15"/>
       <c r="G73" s="15" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="13"/>
       <c r="B74" s="13" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="F74" s="15"/>
       <c r="G74" s="15" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="13"/>
       <c r="B75" s="13" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>1228</v>
-      </c>
-      <c r="D75" s="22" t="s">
-        <v>1072</v>
+        <v>1230</v>
+      </c>
+      <c r="D75" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="F75" s="15" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="G75" s="15"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="13"/>
       <c r="B76" s="13" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="C76" s="13" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D76" s="23" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E76" s="15" t="s">
         <v>1231</v>
       </c>
-      <c r="D76" s="22" t="s">
-        <v>1072</v>
-      </c>
-      <c r="E76" s="15" t="s">
-        <v>1229</v>
-      </c>
       <c r="F76" s="15" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="G76" s="15"/>
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="13"/>
       <c r="B77" s="13" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>1233</v>
-      </c>
-      <c r="D77" s="22" t="s">
-        <v>1072</v>
+        <v>1235</v>
+      </c>
+      <c r="D77" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="F77" s="15" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="G77" s="15"/>
     </row>
     <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="13"/>
       <c r="B78" s="13" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>1235</v>
-      </c>
-      <c r="D78" s="22" t="s">
-        <v>1072</v>
+        <v>1237</v>
+      </c>
+      <c r="D78" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="F78" s="15" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="G78" s="15"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="13"/>
       <c r="B79" s="13" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>1237</v>
-      </c>
-      <c r="D79" s="22" t="s">
-        <v>1072</v>
+        <v>1239</v>
+      </c>
+      <c r="D79" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="F79" s="15" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="G79" s="15"/>
     </row>
     <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="13"/>
       <c r="B80" s="13" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>1239</v>
-      </c>
-      <c r="D80" s="22" t="s">
-        <v>1072</v>
+        <v>1241</v>
+      </c>
+      <c r="D80" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="G80" s="15"/>
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="13"/>
       <c r="B81" s="13" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>1241</v>
-      </c>
-      <c r="D81" s="22" t="s">
-        <v>1072</v>
+        <v>1243</v>
+      </c>
+      <c r="D81" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="F81" s="15" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="G81" s="15"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="13"/>
       <c r="B82" s="13" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>1243</v>
-      </c>
-      <c r="D82" s="22" t="s">
-        <v>1072</v>
+        <v>1245</v>
+      </c>
+      <c r="D82" s="23" t="s">
+        <v>1074</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="G82" s="15"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="13"/>
       <c r="B83" s="13" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F83" s="15"/>
       <c r="G83" s="15"/>
@@ -6296,28 +6302,28 @@
     <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="13"/>
       <c r="B84" s="13" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="F84" s="15"/>
       <c r="G84" s="15" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
@@ -6327,262 +6333,262 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>448</v>
       </c>
       <c r="D88" s="7"/>
       <c r="E88" s="7" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="13" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="D89" s="13"/>
       <c r="E89" s="15" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="F89" s="15" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="G89" s="15" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="17" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="D90" s="17"/>
       <c r="E90" s="19" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="F90" s="19" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="13" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="D91" s="13"/>
       <c r="E91" s="15" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="F91" s="15" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="G91" s="15" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="17" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="D92" s="17"/>
       <c r="E92" s="19" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="F92" s="19" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="G92" s="19" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="13" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="D93" s="13"/>
       <c r="E93" s="15" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="F93" s="15" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="G93" s="15" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="17" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="D94" s="17"/>
       <c r="E94" s="19" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="F94" s="19" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="G94" s="19" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="13" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="D95" s="13"/>
       <c r="E95" s="15" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="F95" s="15" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G95" s="15" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="17" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="C96" s="17" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="D96" s="17"/>
       <c r="E96" s="19" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="F96" s="19" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="G96" s="19" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="13" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="D97" s="13"/>
       <c r="E97" s="15" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="F97" s="15" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="G97" s="15" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="17" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="C98" s="17" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="D98" s="17"/>
       <c r="E98" s="19" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="F98" s="19" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="G98" s="19" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="13" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="D99" s="13"/>
       <c r="E99" s="15" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="F99" s="15" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="G99" s="15" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="10"/>
@@ -6592,11 +6598,11 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="13"/>
-      <c r="B102" s="22" t="s">
-        <v>1121</v>
+      <c r="B102" s="23" t="s">
+        <v>1123</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="D102" s="13"/>
       <c r="E102" s="13"/>
@@ -6605,11 +6611,11 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="13"/>
-      <c r="B103" s="22" t="s">
-        <v>1159</v>
+      <c r="B103" s="23" t="s">
+        <v>1161</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="D103" s="13"/>
       <c r="E103" s="13"/>
@@ -6618,11 +6624,11 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="13"/>
-      <c r="B104" s="22" t="s">
-        <v>1142</v>
+      <c r="B104" s="23" t="s">
+        <v>1144</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="D104" s="13"/>
       <c r="E104" s="13"/>
@@ -6631,11 +6637,11 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="13"/>
-      <c r="B105" s="22" t="s">
-        <v>1153</v>
+      <c r="B105" s="23" t="s">
+        <v>1155</v>
       </c>
       <c r="C105" s="13" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="D105" s="13"/>
       <c r="E105" s="13"/>
@@ -6644,11 +6650,11 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="13"/>
-      <c r="B106" s="22" t="s">
-        <v>1077</v>
+      <c r="B106" s="23" t="s">
+        <v>1079</v>
       </c>
       <c r="C106" s="13" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D106" s="13"/>
       <c r="E106" s="13"/>
@@ -6657,11 +6663,11 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="13"/>
-      <c r="B107" s="22" t="s">
-        <v>1087</v>
+      <c r="B107" s="23" t="s">
+        <v>1089</v>
       </c>
       <c r="C107" s="13" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="D107" s="13"/>
       <c r="E107" s="13"/>
@@ -6670,11 +6676,11 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="13"/>
-      <c r="B108" s="22" t="s">
-        <v>1163</v>
+      <c r="B108" s="23" t="s">
+        <v>1165</v>
       </c>
       <c r="C108" s="13" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="D108" s="13"/>
       <c r="E108" s="13"/>
@@ -6683,11 +6689,11 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="13"/>
-      <c r="B109" s="22" t="s">
-        <v>1105</v>
+      <c r="B109" s="23" t="s">
+        <v>1107</v>
       </c>
       <c r="C109" s="13" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="D109" s="13"/>
       <c r="E109" s="13"/>
@@ -6696,11 +6702,11 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="13"/>
-      <c r="B110" s="22" t="s">
-        <v>1073</v>
+      <c r="B110" s="23" t="s">
+        <v>1075</v>
       </c>
       <c r="C110" s="13" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D110" s="13"/>
       <c r="E110" s="13"/>
@@ -6709,11 +6715,11 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="13"/>
-      <c r="B111" s="22" t="s">
-        <v>1229</v>
+      <c r="B111" s="23" t="s">
+        <v>1231</v>
       </c>
       <c r="C111" s="13" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="D111" s="13"/>
       <c r="E111" s="13"/>
@@ -7136,7 +7142,7 @@
       </c>
       <c r="B40" s="5" t="n">
         <f aca="false">COUNTIF(Popups!$F$5:$F$40,"Built")</f>
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7154,7 +7160,7 @@
       </c>
       <c r="B42" s="5" t="n">
         <f aca="false">COUNTIF(Popups!$F$5:$F$40,"Not built")</f>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7172,7 +7178,7 @@
       </c>
       <c r="B44" s="5" t="n">
         <f aca="false">COUNTIF(Notifications!$G$5:$G$60,"Not built")</f>
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12859,7 +12865,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
         <v>537</v>
       </c>
@@ -12927,43 +12933,43 @@
       <c r="E7" s="13" t="s">
         <v>540</v>
       </c>
-      <c r="F7" s="20" t="s">
-        <v>36</v>
+      <c r="F7" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="G7" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="H7" s="15" t="s">
         <v>552</v>
       </c>
-      <c r="H7" s="15" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="s">
         <v>553</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>554</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>340</v>
       </c>
       <c r="C8" s="17" t="s">
+        <v>554</v>
+      </c>
+      <c r="D8" s="19" t="s">
         <v>555</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="E8" s="17" t="s">
         <v>556</v>
       </c>
-      <c r="E8" s="17" t="s">
-        <v>540</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>36</v>
+      <c r="F8" s="18" t="s">
+        <v>33</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="H8" s="19" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>558</v>
       </c>
@@ -12979,135 +12985,135 @@
       <c r="E9" s="13" t="s">
         <v>540</v>
       </c>
-      <c r="F9" s="20" t="s">
-        <v>36</v>
+      <c r="F9" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
         <v>563</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>388</v>
+        <v>564</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>540</v>
       </c>
-      <c r="F10" s="21" t="s">
-        <v>36</v>
+      <c r="F10" s="18" t="s">
+        <v>33</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>494</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>540</v>
       </c>
-      <c r="F11" s="20" t="s">
-        <v>36</v>
+      <c r="F11" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>525</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>540</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>36</v>
+      <c r="F12" s="18" t="s">
+        <v>33</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>540</v>
       </c>
-      <c r="F13" s="20" t="s">
-        <v>36</v>
+      <c r="F13" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>322</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>582</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>583</v>
@@ -13199,12 +13205,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
         <v>592</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>593</v>
@@ -13213,13 +13219,13 @@
         <v>594</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>595</v>
       </c>
-      <c r="G5" s="22" t="s">
-        <v>34</v>
+      <c r="G5" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>541</v>
@@ -13228,7 +13234,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
         <v>597</v>
       </c>
@@ -13247,199 +13253,199 @@
       <c r="F6" s="17" t="s">
         <v>602</v>
       </c>
-      <c r="G6" s="21" t="s">
-        <v>36</v>
+      <c r="G6" s="17" t="s">
+        <v>603</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>600</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>602</v>
       </c>
-      <c r="G7" s="20" t="s">
-        <v>36</v>
+      <c r="G7" s="13" t="s">
+        <v>603</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>602</v>
       </c>
-      <c r="G8" s="21" t="s">
-        <v>36</v>
+      <c r="G8" s="17" t="s">
+        <v>603</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>617</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>36</v>
+        <v>618</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>603</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>594</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>602</v>
       </c>
-      <c r="G10" s="21" t="s">
-        <v>36</v>
+      <c r="G10" s="17" t="s">
+        <v>603</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>594</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>602</v>
       </c>
-      <c r="G11" s="20" t="s">
-        <v>36</v>
+      <c r="G11" s="13" t="s">
+        <v>603</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>594</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F12" s="17" t="s">
         <v>602</v>
       </c>
-      <c r="G12" s="21" t="s">
-        <v>36</v>
+      <c r="G12" s="17" t="s">
+        <v>603</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>594</v>
@@ -13450,25 +13456,25 @@
       <c r="F13" s="13" t="s">
         <v>602</v>
       </c>
-      <c r="G13" s="20" t="s">
-        <v>36</v>
+      <c r="G13" s="13" t="s">
+        <v>603</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>594</v>
@@ -13479,25 +13485,25 @@
       <c r="F14" s="17" t="s">
         <v>602</v>
       </c>
-      <c r="G14" s="21" t="s">
-        <v>36</v>
+      <c r="G14" s="17" t="s">
+        <v>603</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>594</v>
@@ -13508,52 +13514,52 @@
       <c r="F15" s="13" t="s">
         <v>602</v>
       </c>
-      <c r="G15" s="20" t="s">
-        <v>36</v>
+      <c r="G15" s="13" t="s">
+        <v>603</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="I15" s="15"/>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>594</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>602</v>
       </c>
-      <c r="G16" s="21" t="s">
-        <v>36</v>
+      <c r="G16" s="17" t="s">
+        <v>603</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>594</v>
@@ -13562,27 +13568,27 @@
         <v>601</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>650</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>36</v>
+        <v>651</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>603</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>594</v>
@@ -13593,83 +13599,83 @@
       <c r="F18" s="17" t="s">
         <v>602</v>
       </c>
-      <c r="G18" s="21" t="s">
-        <v>36</v>
+      <c r="G18" s="17" t="s">
+        <v>603</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>594</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>617</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>36</v>
+        <v>618</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>603</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>650</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>36</v>
+        <v>651</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>603</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="I20" s="19" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>594</v>
@@ -13678,45 +13684,45 @@
         <v>601</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>650</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>36</v>
+        <v>651</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>603</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>541</v>
       </c>
       <c r="I22" s="19" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
   </sheetData>
@@ -13754,12 +13760,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -13778,16 +13784,16 @@
         <v>533</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>89</v>
@@ -13801,152 +13807,152 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>541</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>541</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>36</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G8" s="21" t="s">
         <v>36</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>36</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>598</v>
@@ -13955,366 +13961,366 @@
         <v>600</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G10" s="21" t="s">
         <v>36</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>600</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>36</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G12" s="21" t="s">
         <v>36</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>36</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>594</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G14" s="21" t="s">
         <v>36</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>36</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="I15" s="15"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G16" s="21" t="s">
         <v>36</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="I16" s="19"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>36</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>594</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G18" s="21" t="s">
         <v>36</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>36</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G20" s="21" t="s">
         <v>36</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="I20" s="19" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G21" s="20" t="s">
         <v>36</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G22" s="21" t="s">
         <v>36</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="I22" s="19" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
   </sheetData>
@@ -14353,12 +14359,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -14374,19 +14380,19 @@
         <v>531</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>89</v>
@@ -14400,524 +14406,524 @@
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>175</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>541</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>175</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>541</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H7" s="13" t="s">
         <v>541</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>781</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>607</v>
+        <v>783</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>608</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>541</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
+        <v>786</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>787</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>788</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>789</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>608</v>
+      </c>
+      <c r="F9" s="13" t="s">
         <v>784</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>785</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>786</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>787</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>607</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>782</v>
-      </c>
       <c r="G9" s="13" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>541</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>792</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>607</v>
+        <v>794</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>608</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>541</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>541</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>495</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>801</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>607</v>
+        <v>803</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>608</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>541</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>806</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>607</v>
+        <v>808</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>608</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>812</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>607</v>
+        <v>814</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>608</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>541</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>456</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>816</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>607</v>
+        <v>818</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>608</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H15" s="13" t="s">
         <v>541</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
+        <v>821</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>806</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>822</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>823</v>
+      </c>
+      <c r="E16" s="17" t="s">
         <v>819</v>
       </c>
-      <c r="B16" s="17" t="s">
-        <v>804</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>820</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>821</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>817</v>
-      </c>
       <c r="F16" s="17" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>541</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>541</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="I20" s="19" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>466</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H21" s="13" t="s">
         <v>541</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>541</v>
       </c>
       <c r="I22" s="19" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
   </sheetData>
@@ -14955,12 +14961,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -14976,42 +14982,42 @@
         <v>531</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>536</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>89</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>175</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>541</v>
@@ -15019,22 +15025,22 @@
       <c r="F5" s="24"/>
       <c r="G5" s="24"/>
       <c r="H5" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>175</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>541</v>
@@ -15042,22 +15048,22 @@
       <c r="F6" s="24"/>
       <c r="G6" s="24"/>
       <c r="H6" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>541</v>
@@ -15065,22 +15071,22 @@
       <c r="F7" s="24"/>
       <c r="G7" s="24"/>
       <c r="H7" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>541</v>
@@ -15088,45 +15094,45 @@
       <c r="F8" s="24"/>
       <c r="G8" s="24"/>
       <c r="H8" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="24"/>
       <c r="H9" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>541</v>
@@ -15134,114 +15140,114 @@
       <c r="F10" s="24"/>
       <c r="G10" s="24"/>
       <c r="H10" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="F11" s="24"/>
       <c r="G11" s="24"/>
       <c r="H11" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="F12" s="24"/>
       <c r="G12" s="24"/>
       <c r="H12" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="F13" s="24"/>
       <c r="G13" s="24"/>
       <c r="H13" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="F14" s="24"/>
       <c r="G14" s="24"/>
       <c r="H14" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I14" s="24"/>
     </row>
     <row r="15" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>541</v>
@@ -15249,22 +15255,22 @@
       <c r="F15" s="24"/>
       <c r="G15" s="24"/>
       <c r="H15" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I15" s="24"/>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>541</v>
@@ -15272,45 +15278,45 @@
       <c r="F16" s="24"/>
       <c r="G16" s="24"/>
       <c r="H16" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
       <c r="H17" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B18" s="17" t="s">
         <v>495</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>541</v>
@@ -15318,22 +15324,22 @@
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
       <c r="H18" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I18" s="24"/>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>541</v>
@@ -15341,22 +15347,22 @@
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
       <c r="H19" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>541</v>
@@ -15364,45 +15370,45 @@
       <c r="F20" s="24"/>
       <c r="G20" s="24"/>
       <c r="H20" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I20" s="24"/>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>175</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>552</v>
+        <v>699</v>
       </c>
       <c r="F21" s="24"/>
       <c r="G21" s="24"/>
       <c r="H21" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I21" s="24"/>
     </row>
     <row r="22" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>541</v>
@@ -15410,22 +15416,22 @@
       <c r="F22" s="24"/>
       <c r="G22" s="24"/>
       <c r="H22" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I22" s="24"/>
     </row>
     <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>541</v>
@@ -15433,7 +15439,7 @@
       <c r="F23" s="24"/>
       <c r="G23" s="24"/>
       <c r="H23" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I23" s="24"/>
     </row>
@@ -15475,12 +15481,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -15498,776 +15504,776 @@
         <v>531</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>89</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J5" s="24"/>
       <c r="K5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C6" s="19" t="s">
+        <v>936</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>929</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>937</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>931</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>938</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>939</v>
+      </c>
+      <c r="I6" s="25" t="s">
         <v>934</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>927</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>935</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>929</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>936</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>937</v>
-      </c>
-      <c r="I6" s="25" t="s">
-        <v>932</v>
       </c>
       <c r="J6" s="24"/>
       <c r="K6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J7" s="24"/>
       <c r="K7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>242</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J8" s="24"/>
       <c r="K8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>242</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J9" s="24"/>
       <c r="K9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>242</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="G10" s="19" t="s">
         <v>253</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J10" s="24"/>
       <c r="K10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>242</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J11" s="24"/>
       <c r="K11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>242</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J12" s="24"/>
       <c r="K12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>242</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J13" s="24"/>
       <c r="K13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>242</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J14" s="24"/>
       <c r="K14" s="24"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>242</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J15" s="24"/>
       <c r="K15" s="24"/>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="I16" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J16" s="24"/>
       <c r="K16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="I17" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J17" s="24"/>
       <c r="K17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="G18" s="19" t="s">
         <v>169</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J18" s="24"/>
       <c r="K18" s="24"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="G19" s="15" t="s">
         <v>169</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="I19" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J19" s="24"/>
       <c r="K19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="G20" s="19" t="s">
         <v>209</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J20" s="24"/>
       <c r="K20" s="24"/>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>145</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="G21" s="15" t="s">
         <v>143</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="I21" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J21" s="24"/>
       <c r="K21" s="24"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="I22" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J22" s="24"/>
       <c r="K22" s="24"/>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="G23" s="15" t="s">
         <v>328</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="I23" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J23" s="24"/>
       <c r="K23" s="24"/>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="B24" s="17" t="s">
         <v>370</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="G24" s="19" t="s">
         <v>151</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="I24" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J24" s="24"/>
       <c r="K24" s="24"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="B25" s="13" t="s">
         <v>370</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="I25" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J25" s="24"/>
       <c r="K25" s="24"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="G26" s="19" t="s">
         <v>147</v>
       </c>
       <c r="H26" s="19" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="I26" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J26" s="24"/>
       <c r="K26" s="24"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="I27" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J27" s="24"/>
       <c r="K27" s="24"/>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="B28" s="17" t="s">
         <v>175</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="H28" s="19" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="I28" s="25" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J28" s="24"/>
       <c r="K28" s="24"/>
